--- a/ONCHO/Impact Assessments/Nigeria/2025/river states ia/ng_oncho_stop_2507_3_rdtov16_ia_rs.xlsx
+++ b/ONCHO/Impact Assessments/Nigeria/2025/river states ia/ng_oncho_stop_2507_3_rdtov16_ia_rs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2024\cross river\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river states ia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22358062-20EF-4128-85D5-B50162D0C007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B72AFF9-C5B1-49CB-9504-55D3ADACD375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="234">
   <si>
     <t>type</t>
   </si>
@@ -324,175 +324,406 @@
     <t>ELISA - Final decision</t>
   </si>
   <si>
-    <t>CROSS RIVER</t>
-  </si>
-  <si>
-    <t>ABI</t>
-  </si>
-  <si>
-    <t>AKAMKPA</t>
-  </si>
-  <si>
-    <t>BOKI</t>
-  </si>
-  <si>
-    <t>OGOJA</t>
-  </si>
-  <si>
-    <t>YAKURR</t>
-  </si>
-  <si>
-    <t>AFAFANYI</t>
-  </si>
-  <si>
-    <t>AKPOHA-IGBO</t>
-  </si>
-  <si>
-    <t>BAZOHURE</t>
-  </si>
-  <si>
-    <t>IGBO EMABAN</t>
-  </si>
-  <si>
-    <t>IJOM</t>
-  </si>
-  <si>
-    <t>IMINA</t>
-  </si>
-  <si>
-    <t>ITIGIDI</t>
-  </si>
-  <si>
-    <t>IYOGUE</t>
-  </si>
-  <si>
-    <t>AKING</t>
-  </si>
-  <si>
-    <t>AKWA IBAMI</t>
-  </si>
-  <si>
-    <t>EKANG</t>
-  </si>
-  <si>
-    <t>EKONG</t>
-  </si>
-  <si>
-    <t>MFAMOSING</t>
-  </si>
-  <si>
-    <t>OKWA 11</t>
-  </si>
-  <si>
-    <t>OKENDE IDP CAMP</t>
-  </si>
-  <si>
-    <t>AGOI IBAMI</t>
-  </si>
-  <si>
-    <t>CRS_AKA_M_001</t>
-  </si>
-  <si>
-    <t>CRS_AKA_M_002</t>
-  </si>
-  <si>
-    <t>CRS_AKA_M_003</t>
-  </si>
-  <si>
-    <t>CRS_AKA_M_004</t>
-  </si>
-  <si>
-    <t>CRS_AKA_M_005</t>
-  </si>
-  <si>
-    <t>CRS_BOK_M_006</t>
-  </si>
-  <si>
-    <t>CRS_OGO_M_007</t>
-  </si>
-  <si>
-    <t>CRS_YAK_M_008</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_001</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_002</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_003</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_004</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_005</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_006</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_007</t>
-  </si>
-  <si>
-    <t>CRS_ABI_IA_008</t>
-  </si>
-  <si>
-    <t>CALABAR_SOUTH</t>
-  </si>
-  <si>
-    <t>AKPABUYO</t>
-  </si>
-  <si>
-    <t>ANANTIGHA</t>
-  </si>
-  <si>
-    <t>EFUT STREET</t>
-  </si>
-  <si>
-    <t>EKPENE ESUK</t>
-  </si>
-  <si>
-    <t>ELIOTT POINT</t>
-  </si>
-  <si>
-    <t>PARROT CROSSING</t>
-  </si>
-  <si>
-    <t>SMOKE FLATS</t>
-  </si>
-  <si>
-    <t>TECH SCHOOL ROAD</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_017</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_018</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_019</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_020</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_021</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_022</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_023</t>
-  </si>
-  <si>
-    <t>CRS_CAS_IA_024</t>
-  </si>
-  <si>
     <t>(Cross River 2024 Nov) - 3. ELISA Form V2.2</t>
   </si>
   <si>
     <t>ng_oncho_stop_2411_3_rdtov16_cs_v2_2</t>
+  </si>
+  <si>
+    <t>RIVERS</t>
+  </si>
+  <si>
+    <t>AHOADA EAST</t>
+  </si>
+  <si>
+    <t>AKUKU TORU</t>
+  </si>
+  <si>
+    <t>ANDONI</t>
+  </si>
+  <si>
+    <t>ASARI-TORU</t>
+  </si>
+  <si>
+    <t>BONNY</t>
+  </si>
+  <si>
+    <t>DEGEMA</t>
+  </si>
+  <si>
+    <t>ETCHE</t>
+  </si>
+  <si>
+    <t>IKWERRE</t>
+  </si>
+  <si>
+    <t>OGU/BOLO</t>
+  </si>
+  <si>
+    <t>OKRIKA</t>
+  </si>
+  <si>
+    <t>OMUMMA</t>
+  </si>
+  <si>
+    <t>OPOBO/NKORO</t>
+  </si>
+  <si>
+    <t>AHOADA MAIN TOWN</t>
+  </si>
+  <si>
+    <t>IHUABA</t>
+  </si>
+  <si>
+    <t>IHUOWO</t>
+  </si>
+  <si>
+    <t>ODEKE</t>
+  </si>
+  <si>
+    <t>OGBELE</t>
+  </si>
+  <si>
+    <t>ABONNEMA</t>
+  </si>
+  <si>
+    <t>BRIGGS</t>
+  </si>
+  <si>
+    <t>NEW SITE</t>
+  </si>
+  <si>
+    <t>OBONOMA</t>
+  </si>
+  <si>
+    <t>OGONIMA</t>
+  </si>
+  <si>
+    <t>ASARAMA</t>
+  </si>
+  <si>
+    <t>EBUKUMA</t>
+  </si>
+  <si>
+    <t>IKURU</t>
+  </si>
+  <si>
+    <t>INYONG-ORON</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>ABALAMA</t>
+  </si>
+  <si>
+    <t>BUGUMA</t>
+  </si>
+  <si>
+    <t>KRAKRAMA</t>
+  </si>
+  <si>
+    <t>SAMA</t>
+  </si>
+  <si>
+    <t>TEMA</t>
+  </si>
+  <si>
+    <t>ABALAMABIE JUMBO/GEORGE TOLOFARI</t>
+  </si>
+  <si>
+    <t>AKIAMA</t>
+  </si>
+  <si>
+    <t>FINIMA</t>
+  </si>
+  <si>
+    <t>MARCULAY</t>
+  </si>
+  <si>
+    <t>OROSIKRI</t>
+  </si>
+  <si>
+    <t>EZI-USUMBLO</t>
+  </si>
+  <si>
+    <t>OBUAMA</t>
+  </si>
+  <si>
+    <t>OKUDEKE</t>
+  </si>
+  <si>
+    <t>USOKUN</t>
+  </si>
+  <si>
+    <t>UMUATURU</t>
+  </si>
+  <si>
+    <t>UMUOCHARM</t>
+  </si>
+  <si>
+    <t>UMUOGA</t>
+  </si>
+  <si>
+    <t>UMUOKOROGBADIM</t>
+  </si>
+  <si>
+    <t>UMUOTAMIRI</t>
+  </si>
+  <si>
+    <t>FULANI COMMUNITY/BARRACK</t>
+  </si>
+  <si>
+    <t>OGBODO ISIOKPO</t>
+  </si>
+  <si>
+    <t>OMUEWEI IGWUKUTA</t>
+  </si>
+  <si>
+    <t>OMUEZE OMUANWA</t>
+  </si>
+  <si>
+    <t>OMUWECHI</t>
+  </si>
+  <si>
+    <t>BOLO</t>
+  </si>
+  <si>
+    <t>CHUKU-AMA</t>
+  </si>
+  <si>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>OGU</t>
+  </si>
+  <si>
+    <t>WAKAMA</t>
+  </si>
+  <si>
+    <t>ANYUNGUBIRI</t>
+  </si>
+  <si>
+    <t>DAKAAMA</t>
+  </si>
+  <si>
+    <t>GREAM-AMA</t>
+  </si>
+  <si>
+    <t>KALANGABIRI</t>
+  </si>
+  <si>
+    <t>OGBOGBO</t>
+  </si>
+  <si>
+    <t>AMAJI</t>
+  </si>
+  <si>
+    <t>EBERI</t>
+  </si>
+  <si>
+    <t>UMUELECHI</t>
+  </si>
+  <si>
+    <t>UMUNWAKA</t>
+  </si>
+  <si>
+    <t>UMUOKPURUKPU</t>
+  </si>
+  <si>
+    <t>BROWN</t>
+  </si>
+  <si>
+    <t>FUBARA</t>
+  </si>
+  <si>
+    <t>KALAIBIAMA</t>
+  </si>
+  <si>
+    <t>NKORO</t>
+  </si>
+  <si>
+    <t>OGOLO</t>
+  </si>
+  <si>
+    <t>RIV_AHE_M_001</t>
+  </si>
+  <si>
+    <t>RIV_AHE_M_002</t>
+  </si>
+  <si>
+    <t>RIV_AHE_M_003</t>
+  </si>
+  <si>
+    <t>RIV_AHE_M_004</t>
+  </si>
+  <si>
+    <t>RIV_AHE_M_005</t>
+  </si>
+  <si>
+    <t>RIV_AKT_M_006</t>
+  </si>
+  <si>
+    <t>RIV_AKT_M_007</t>
+  </si>
+  <si>
+    <t>RIV_AKT_M_113</t>
+  </si>
+  <si>
+    <t>RIV_AKT_M_114</t>
+  </si>
+  <si>
+    <t>RIV_AKT_M_115</t>
+  </si>
+  <si>
+    <t>RIV_AND_M_008</t>
+  </si>
+  <si>
+    <t>RIV_AND_M_009</t>
+  </si>
+  <si>
+    <t>RIV_AND_M_010</t>
+  </si>
+  <si>
+    <t>RIV_AND_M_011</t>
+  </si>
+  <si>
+    <t>RIV_AND_M_012</t>
+  </si>
+  <si>
+    <t>RIV_AST_M_013</t>
+  </si>
+  <si>
+    <t>RIV_AST_M_014</t>
+  </si>
+  <si>
+    <t>RIV_AST_M_015</t>
+  </si>
+  <si>
+    <t>RIV_AST_M_016</t>
+  </si>
+  <si>
+    <t>RIV_AST_M_017</t>
+  </si>
+  <si>
+    <t>RIV_BON_M_018</t>
+  </si>
+  <si>
+    <t>RIV_BON_M_019</t>
+  </si>
+  <si>
+    <t>RIV_BON_M_020</t>
+  </si>
+  <si>
+    <t>RIV_BON_M_021</t>
+  </si>
+  <si>
+    <t>RIV_BON_M_022</t>
+  </si>
+  <si>
+    <t>RIV_DEG_M_023</t>
+  </si>
+  <si>
+    <t>RIV_DEG_M_024</t>
+  </si>
+  <si>
+    <t>RIV_DEG_M_025</t>
+  </si>
+  <si>
+    <t>RIV_DEG_M_111</t>
+  </si>
+  <si>
+    <t>RIV_DEG_M_112</t>
+  </si>
+  <si>
+    <t>RIV_ETC_M_026</t>
+  </si>
+  <si>
+    <t>RIV_ETC_M_027</t>
+  </si>
+  <si>
+    <t>RIV_ETC_M_028</t>
+  </si>
+  <si>
+    <t>RIV_ETC_M_029</t>
+  </si>
+  <si>
+    <t>RIV_ETC_M_030</t>
+  </si>
+  <si>
+    <t>RIV_IKW_M_031</t>
+  </si>
+  <si>
+    <t>RIV_IKW_M_032</t>
+  </si>
+  <si>
+    <t>RIV_IKW_M_033</t>
+  </si>
+  <si>
+    <t>RIV_IKW_M_034</t>
+  </si>
+  <si>
+    <t>RIV_IKW_M_035</t>
+  </si>
+  <si>
+    <t>RIV_OGB_M_036</t>
+  </si>
+  <si>
+    <t>RIV_OGB_M_037</t>
+  </si>
+  <si>
+    <t>RIV_OGB_M_038</t>
+  </si>
+  <si>
+    <t>RIV_OGB_M_039</t>
+  </si>
+  <si>
+    <t>RIV_OGB_M_040</t>
+  </si>
+  <si>
+    <t>RIV_OKR_M_041</t>
+  </si>
+  <si>
+    <t>RIV_OKR_M_042</t>
+  </si>
+  <si>
+    <t>RIV_OKR_M_043</t>
+  </si>
+  <si>
+    <t>RIV_OKR_M_044</t>
+  </si>
+  <si>
+    <t>RIV_OKR_M_045</t>
+  </si>
+  <si>
+    <t>RIV_OMU_M_046</t>
+  </si>
+  <si>
+    <t>RIV_OMU_M_047</t>
+  </si>
+  <si>
+    <t>RIV_OMU_M_048</t>
+  </si>
+  <si>
+    <t>RIV_OMU_M_049</t>
+  </si>
+  <si>
+    <t>RIV_OMU_M_050</t>
+  </si>
+  <si>
+    <t>RIV_OPN_M_051</t>
+  </si>
+  <si>
+    <t>RIV_OPN_M_052</t>
+  </si>
+  <si>
+    <t>RIV_OPN_M_053</t>
+  </si>
+  <si>
+    <t>RIV_OPN_M_054</t>
+  </si>
+  <si>
+    <t>RIV_OPN_M_055</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1594,10 +1825,10 @@
         <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1605,13 +1836,13 @@
         <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1619,13 +1850,13 @@
         <v>55</v>
       </c>
       <c r="B27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1633,13 +1864,13 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1647,13 +1878,13 @@
         <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1661,13 +1892,13 @@
         <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1675,111 +1906,114 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" t="s">
-        <v>101</v>
+        <v>110</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" t="s">
-        <v>101</v>
+        <v>111</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>101</v>
+        <v>112</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>101</v>
+        <v>113</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" t="s">
-        <v>101</v>
+        <v>114</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" t="s">
-        <v>101</v>
-      </c>
+      <c r="D38" s="21"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1787,13 +2021,13 @@
         <v>56</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1801,13 +2035,13 @@
         <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1815,13 +2049,13 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1829,13 +2063,13 @@
         <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1843,13 +2077,13 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1857,13 +2091,13 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1871,13 +2105,13 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1885,13 +2119,13 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E47" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1899,464 +2133,1553 @@
         <v>56</v>
       </c>
       <c r="B48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" t="s">
+        <v>124</v>
+      </c>
+      <c r="E48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" t="s">
+        <v>125</v>
+      </c>
+      <c r="E49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" t="s">
+        <v>129</v>
+      </c>
+      <c r="E53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" t="s">
+        <v>130</v>
+      </c>
+      <c r="C54" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" t="s">
+        <v>138</v>
+      </c>
+      <c r="E62" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" t="s">
+        <v>139</v>
+      </c>
+      <c r="E63" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" t="s">
         <v>140</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C65" t="s">
         <v>140</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E65" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>56</v>
+      </c>
+      <c r="B66" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" t="s">
+        <v>142</v>
+      </c>
+      <c r="E67" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" t="s">
+        <v>143</v>
+      </c>
+      <c r="C68" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>56</v>
+      </c>
+      <c r="B69" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70" t="s">
+        <v>145</v>
+      </c>
+      <c r="E70" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>56</v>
+      </c>
+      <c r="B71" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>56</v>
+      </c>
+      <c r="B72" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" t="s">
+        <v>147</v>
+      </c>
+      <c r="E72" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B73" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" t="s">
+        <v>148</v>
+      </c>
+      <c r="E73" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>56</v>
+      </c>
+      <c r="B74" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" t="s">
+        <v>149</v>
+      </c>
+      <c r="E74" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" t="s">
+        <v>150</v>
+      </c>
+      <c r="E75" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" t="s">
+        <v>151</v>
+      </c>
+      <c r="C76" t="s">
+        <v>151</v>
+      </c>
+      <c r="E76" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" t="s">
+        <v>152</v>
+      </c>
+      <c r="E77" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>56</v>
+      </c>
+      <c r="B78" t="s">
+        <v>153</v>
+      </c>
+      <c r="C78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>56</v>
+      </c>
+      <c r="B79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C79" t="s">
+        <v>154</v>
+      </c>
+      <c r="E79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>56</v>
+      </c>
+      <c r="B80" t="s">
+        <v>155</v>
+      </c>
+      <c r="C80" t="s">
+        <v>155</v>
+      </c>
+      <c r="E80" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>56</v>
+      </c>
+      <c r="B81" t="s">
+        <v>156</v>
+      </c>
+      <c r="C81" t="s">
+        <v>156</v>
+      </c>
+      <c r="E81" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>56</v>
+      </c>
+      <c r="B82" t="s">
+        <v>157</v>
+      </c>
+      <c r="C82" t="s">
+        <v>157</v>
+      </c>
+      <c r="E82" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>56</v>
+      </c>
+      <c r="B83" t="s">
+        <v>158</v>
+      </c>
+      <c r="C83" t="s">
+        <v>158</v>
+      </c>
+      <c r="E83" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>56</v>
+      </c>
+      <c r="B84" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" t="s">
+        <v>159</v>
+      </c>
+      <c r="E84" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>56</v>
+      </c>
+      <c r="B85" t="s">
+        <v>160</v>
+      </c>
+      <c r="C85" t="s">
+        <v>160</v>
+      </c>
+      <c r="E85" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>56</v>
+      </c>
+      <c r="B86" t="s">
+        <v>161</v>
+      </c>
+      <c r="C86" t="s">
+        <v>161</v>
+      </c>
+      <c r="E86" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>56</v>
+      </c>
+      <c r="B87" t="s">
+        <v>162</v>
+      </c>
+      <c r="C87" t="s">
+        <v>162</v>
+      </c>
+      <c r="E87" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>56</v>
+      </c>
+      <c r="B88" t="s">
+        <v>163</v>
+      </c>
+      <c r="C88" t="s">
+        <v>163</v>
+      </c>
+      <c r="E88" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>56</v>
+      </c>
+      <c r="B89" t="s">
+        <v>164</v>
+      </c>
+      <c r="C89" t="s">
+        <v>164</v>
+      </c>
+      <c r="E89" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>56</v>
+      </c>
+      <c r="B90" t="s">
+        <v>165</v>
+      </c>
+      <c r="C90" t="s">
+        <v>165</v>
+      </c>
+      <c r="E90" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>56</v>
+      </c>
+      <c r="B91" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" t="s">
+        <v>166</v>
+      </c>
+      <c r="E91" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>56</v>
+      </c>
+      <c r="B92" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" t="s">
+        <v>167</v>
+      </c>
+      <c r="E92" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93" t="s">
+        <v>168</v>
+      </c>
+      <c r="C93" t="s">
+        <v>168</v>
+      </c>
+      <c r="E93" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>56</v>
+      </c>
+      <c r="B94" t="s">
+        <v>169</v>
+      </c>
+      <c r="C94" t="s">
+        <v>169</v>
+      </c>
+      <c r="E94" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>56</v>
+      </c>
+      <c r="B95" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" t="s">
+        <v>170</v>
+      </c>
+      <c r="E95" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>56</v>
+      </c>
+      <c r="B96" t="s">
+        <v>171</v>
+      </c>
+      <c r="C96" t="s">
+        <v>171</v>
+      </c>
+      <c r="E96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>56</v>
+      </c>
+      <c r="B97" t="s">
+        <v>172</v>
+      </c>
+      <c r="C97" t="s">
+        <v>172</v>
+      </c>
+      <c r="E97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>56</v>
+      </c>
+      <c r="B98" t="s">
+        <v>173</v>
+      </c>
+      <c r="C98" t="s">
+        <v>173</v>
+      </c>
+      <c r="E98" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>88</v>
+      </c>
+      <c r="B100" t="s">
+        <v>174</v>
+      </c>
+      <c r="C100" t="s">
+        <v>174</v>
+      </c>
+      <c r="F100" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>88</v>
+      </c>
+      <c r="B101" t="s">
+        <v>175</v>
+      </c>
+      <c r="C101" t="s">
+        <v>175</v>
+      </c>
+      <c r="F101" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>88</v>
+      </c>
+      <c r="B102" t="s">
+        <v>176</v>
+      </c>
+      <c r="C102" t="s">
+        <v>176</v>
+      </c>
+      <c r="F102" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>88</v>
+      </c>
+      <c r="B103" t="s">
+        <v>177</v>
+      </c>
+      <c r="C103" t="s">
+        <v>177</v>
+      </c>
+      <c r="F103" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>88</v>
+      </c>
+      <c r="B104" t="s">
+        <v>178</v>
+      </c>
+      <c r="C104" t="s">
+        <v>178</v>
+      </c>
+      <c r="F104" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>88</v>
+      </c>
+      <c r="B105" t="s">
+        <v>179</v>
+      </c>
+      <c r="C105" t="s">
+        <v>179</v>
+      </c>
+      <c r="F105" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>88</v>
+      </c>
+      <c r="B106" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" t="s">
+        <v>180</v>
+      </c>
+      <c r="F106" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>88</v>
+      </c>
+      <c r="B107" t="s">
+        <v>181</v>
+      </c>
+      <c r="C107" t="s">
+        <v>181</v>
+      </c>
+      <c r="F107" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>88</v>
+      </c>
+      <c r="B108" t="s">
+        <v>182</v>
+      </c>
+      <c r="C108" t="s">
+        <v>182</v>
+      </c>
+      <c r="F108" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>88</v>
+      </c>
+      <c r="B109" t="s">
+        <v>183</v>
+      </c>
+      <c r="C109" t="s">
+        <v>183</v>
+      </c>
+      <c r="F109" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>88</v>
+      </c>
+      <c r="B110" t="s">
+        <v>184</v>
+      </c>
+      <c r="C110" t="s">
+        <v>184</v>
+      </c>
+      <c r="F110" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>88</v>
+      </c>
+      <c r="B111" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" t="s">
+        <v>185</v>
+      </c>
+      <c r="F111" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>88</v>
+      </c>
+      <c r="B112" t="s">
+        <v>186</v>
+      </c>
+      <c r="C112" t="s">
+        <v>186</v>
+      </c>
+      <c r="F112" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>88</v>
+      </c>
+      <c r="B113" t="s">
+        <v>187</v>
+      </c>
+      <c r="C113" t="s">
+        <v>187</v>
+      </c>
+      <c r="F113" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>88</v>
+      </c>
+      <c r="B114" t="s">
+        <v>188</v>
+      </c>
+      <c r="C114" t="s">
+        <v>188</v>
+      </c>
+      <c r="F114" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>88</v>
+      </c>
+      <c r="B115" t="s">
+        <v>189</v>
+      </c>
+      <c r="C115" t="s">
+        <v>189</v>
+      </c>
+      <c r="F115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>88</v>
+      </c>
+      <c r="B116" t="s">
+        <v>190</v>
+      </c>
+      <c r="C116" t="s">
+        <v>190</v>
+      </c>
+      <c r="F116" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>88</v>
+      </c>
+      <c r="B117" t="s">
+        <v>191</v>
+      </c>
+      <c r="C117" t="s">
+        <v>191</v>
+      </c>
+      <c r="F117" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>88</v>
+      </c>
+      <c r="B118" t="s">
+        <v>192</v>
+      </c>
+      <c r="C118" t="s">
+        <v>192</v>
+      </c>
+      <c r="F118" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>88</v>
+      </c>
+      <c r="B119" t="s">
+        <v>193</v>
+      </c>
+      <c r="C119" t="s">
+        <v>193</v>
+      </c>
+      <c r="F119" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>88</v>
+      </c>
+      <c r="B120" t="s">
+        <v>194</v>
+      </c>
+      <c r="C120" t="s">
+        <v>194</v>
+      </c>
+      <c r="F120" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>88</v>
+      </c>
+      <c r="B121" t="s">
+        <v>195</v>
+      </c>
+      <c r="C121" t="s">
+        <v>195</v>
+      </c>
+      <c r="F121" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" t="s">
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>88</v>
+      </c>
+      <c r="B122" t="s">
+        <v>196</v>
+      </c>
+      <c r="C122" t="s">
+        <v>196</v>
+      </c>
+      <c r="F122" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>88</v>
+      </c>
+      <c r="B123" t="s">
+        <v>197</v>
+      </c>
+      <c r="C123" t="s">
+        <v>197</v>
+      </c>
+      <c r="F123" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>88</v>
+      </c>
+      <c r="B124" t="s">
+        <v>198</v>
+      </c>
+      <c r="C124" t="s">
+        <v>198</v>
+      </c>
+      <c r="F124" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>88</v>
+      </c>
+      <c r="B125" t="s">
+        <v>199</v>
+      </c>
+      <c r="C125" t="s">
+        <v>199</v>
+      </c>
+      <c r="F125" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>88</v>
+      </c>
+      <c r="B126" t="s">
+        <v>200</v>
+      </c>
+      <c r="C126" t="s">
+        <v>200</v>
+      </c>
+      <c r="F126" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>88</v>
+      </c>
+      <c r="B127" t="s">
+        <v>201</v>
+      </c>
+      <c r="C127" t="s">
+        <v>201</v>
+      </c>
+      <c r="F127" t="s">
         <v>141</v>
       </c>
-      <c r="C49" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" t="s">
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>88</v>
+      </c>
+      <c r="B128" t="s">
+        <v>202</v>
+      </c>
+      <c r="C128" t="s">
+        <v>202</v>
+      </c>
+      <c r="F128" t="s">
         <v>142</v>
       </c>
-      <c r="C50" t="s">
-        <v>142</v>
-      </c>
-      <c r="E50" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" t="s">
-        <v>143</v>
-      </c>
-      <c r="C51" t="s">
-        <v>143</v>
-      </c>
-      <c r="E51" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>88</v>
+      </c>
+      <c r="B129" t="s">
+        <v>203</v>
+      </c>
+      <c r="C129" t="s">
+        <v>203</v>
+      </c>
+      <c r="F129" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>88</v>
+      </c>
+      <c r="B130" t="s">
+        <v>204</v>
+      </c>
+      <c r="C130" t="s">
+        <v>204</v>
+      </c>
+      <c r="F130" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>88</v>
+      </c>
+      <c r="B131" t="s">
+        <v>205</v>
+      </c>
+      <c r="C131" t="s">
+        <v>205</v>
+      </c>
+      <c r="F131" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>88</v>
+      </c>
+      <c r="B132" t="s">
+        <v>206</v>
+      </c>
+      <c r="C132" t="s">
+        <v>206</v>
+      </c>
+      <c r="F132" t="s">
         <v>144</v>
       </c>
-      <c r="C52" t="s">
-        <v>144</v>
-      </c>
-      <c r="E52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" t="s">
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>88</v>
+      </c>
+      <c r="B133" t="s">
+        <v>207</v>
+      </c>
+      <c r="C133" t="s">
+        <v>207</v>
+      </c>
+      <c r="F133" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>88</v>
+      </c>
+      <c r="B134" t="s">
+        <v>208</v>
+      </c>
+      <c r="C134" t="s">
+        <v>208</v>
+      </c>
+      <c r="F134" t="s">
         <v>145</v>
       </c>
-      <c r="C53" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" t="s">
-        <v>146</v>
-      </c>
-      <c r="C54" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" t="s">
-        <v>120</v>
-      </c>
-      <c r="E55" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" t="s">
-        <v>121</v>
-      </c>
-      <c r="C56" t="s">
-        <v>121</v>
-      </c>
-      <c r="E56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="10"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B58" t="s">
-        <v>122</v>
-      </c>
-      <c r="C58" t="s">
-        <v>122</v>
-      </c>
-      <c r="F58" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B59" t="s">
-        <v>123</v>
-      </c>
-      <c r="C59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F59" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B60" t="s">
-        <v>124</v>
-      </c>
-      <c r="C60" t="s">
-        <v>124</v>
-      </c>
-      <c r="F60" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B61" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" t="s">
-        <v>125</v>
-      </c>
-      <c r="F61" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B62" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" t="s">
-        <v>126</v>
-      </c>
-      <c r="F62" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B63" t="s">
-        <v>127</v>
-      </c>
-      <c r="C63" t="s">
-        <v>127</v>
-      </c>
-      <c r="F63" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B64" t="s">
-        <v>128</v>
-      </c>
-      <c r="C64" t="s">
-        <v>128</v>
-      </c>
-      <c r="F64" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
-        <v>88</v>
-      </c>
-      <c r="B65" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" t="s">
-        <v>129</v>
-      </c>
-      <c r="F65" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
-        <v>88</v>
-      </c>
-      <c r="B66" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" t="s">
-        <v>130</v>
-      </c>
-      <c r="F66" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
-        <v>88</v>
-      </c>
-      <c r="B67" t="s">
-        <v>131</v>
-      </c>
-      <c r="C67" t="s">
-        <v>131</v>
-      </c>
-      <c r="F67" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
-        <v>88</v>
-      </c>
-      <c r="B68" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" t="s">
-        <v>132</v>
-      </c>
-      <c r="F68" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
-        <v>88</v>
-      </c>
-      <c r="B69" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" t="s">
-        <v>133</v>
-      </c>
-      <c r="F69" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
-        <v>88</v>
-      </c>
-      <c r="B70" t="s">
-        <v>134</v>
-      </c>
-      <c r="C70" t="s">
-        <v>134</v>
-      </c>
-      <c r="F70" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
-        <v>88</v>
-      </c>
-      <c r="B71" t="s">
-        <v>135</v>
-      </c>
-      <c r="C71" t="s">
-        <v>135</v>
-      </c>
-      <c r="F71" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
-        <v>88</v>
-      </c>
-      <c r="B72" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" t="s">
-        <v>136</v>
-      </c>
-      <c r="F72" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B73" t="s">
-        <v>137</v>
-      </c>
-      <c r="C73" t="s">
-        <v>137</v>
-      </c>
-      <c r="F73" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
-        <v>88</v>
-      </c>
-      <c r="B74" t="s">
-        <v>147</v>
-      </c>
-      <c r="C74" t="s">
-        <v>147</v>
-      </c>
-      <c r="F74" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
-        <v>88</v>
-      </c>
-      <c r="B75" t="s">
-        <v>148</v>
-      </c>
-      <c r="C75" t="s">
-        <v>148</v>
-      </c>
-      <c r="F75" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
-        <v>88</v>
-      </c>
-      <c r="B76" t="s">
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>88</v>
+      </c>
+      <c r="B135" t="s">
+        <v>209</v>
+      </c>
+      <c r="C135" t="s">
+        <v>209</v>
+      </c>
+      <c r="F135" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>88</v>
+      </c>
+      <c r="B136" t="s">
+        <v>210</v>
+      </c>
+      <c r="C136" t="s">
+        <v>210</v>
+      </c>
+      <c r="F136" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>88</v>
+      </c>
+      <c r="B137" t="s">
+        <v>211</v>
+      </c>
+      <c r="C137" t="s">
+        <v>211</v>
+      </c>
+      <c r="F137" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>88</v>
+      </c>
+      <c r="B138" t="s">
+        <v>212</v>
+      </c>
+      <c r="C138" t="s">
+        <v>212</v>
+      </c>
+      <c r="F138" t="s">
         <v>149</v>
       </c>
-      <c r="C76" t="s">
-        <v>149</v>
-      </c>
-      <c r="F76" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
-        <v>88</v>
-      </c>
-      <c r="B77" t="s">
-        <v>150</v>
-      </c>
-      <c r="C77" t="s">
-        <v>150</v>
-      </c>
-      <c r="F77" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
-        <v>88</v>
-      </c>
-      <c r="B78" t="s">
-        <v>151</v>
-      </c>
-      <c r="C78" t="s">
-        <v>151</v>
-      </c>
-      <c r="F78" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
-        <v>88</v>
-      </c>
-      <c r="B79" t="s">
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>88</v>
+      </c>
+      <c r="B139" t="s">
+        <v>213</v>
+      </c>
+      <c r="C139" t="s">
+        <v>213</v>
+      </c>
+      <c r="F139" t="s">
         <v>152</v>
       </c>
-      <c r="C79" t="s">
-        <v>152</v>
-      </c>
-      <c r="F79" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" t="s">
-        <v>153</v>
-      </c>
-      <c r="C80" t="s">
-        <v>153</v>
-      </c>
-      <c r="F80" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" t="s">
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>88</v>
+      </c>
+      <c r="B140" t="s">
+        <v>214</v>
+      </c>
+      <c r="C140" t="s">
+        <v>214</v>
+      </c>
+      <c r="F140" t="s">
         <v>154</v>
       </c>
-      <c r="C81" t="s">
-        <v>154</v>
-      </c>
-      <c r="F81" t="s">
-        <v>146</v>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>88</v>
+      </c>
+      <c r="B141" t="s">
+        <v>215</v>
+      </c>
+      <c r="C141" t="s">
+        <v>215</v>
+      </c>
+      <c r="F141" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>88</v>
+      </c>
+      <c r="B142" t="s">
+        <v>216</v>
+      </c>
+      <c r="C142" t="s">
+        <v>216</v>
+      </c>
+      <c r="F142" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>88</v>
+      </c>
+      <c r="B143" t="s">
+        <v>217</v>
+      </c>
+      <c r="C143" t="s">
+        <v>217</v>
+      </c>
+      <c r="F143" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>88</v>
+      </c>
+      <c r="B144" t="s">
+        <v>218</v>
+      </c>
+      <c r="C144" t="s">
+        <v>218</v>
+      </c>
+      <c r="F144" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>88</v>
+      </c>
+      <c r="B145" t="s">
+        <v>219</v>
+      </c>
+      <c r="C145" t="s">
+        <v>219</v>
+      </c>
+      <c r="F145" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>88</v>
+      </c>
+      <c r="B146" t="s">
+        <v>220</v>
+      </c>
+      <c r="C146" t="s">
+        <v>220</v>
+      </c>
+      <c r="F146" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>88</v>
+      </c>
+      <c r="B147" t="s">
+        <v>221</v>
+      </c>
+      <c r="C147" t="s">
+        <v>221</v>
+      </c>
+      <c r="F147" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>88</v>
+      </c>
+      <c r="B148" t="s">
+        <v>222</v>
+      </c>
+      <c r="C148" t="s">
+        <v>222</v>
+      </c>
+      <c r="F148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>88</v>
+      </c>
+      <c r="B149" t="s">
+        <v>223</v>
+      </c>
+      <c r="C149" t="s">
+        <v>223</v>
+      </c>
+      <c r="F149" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>88</v>
+      </c>
+      <c r="B150" t="s">
+        <v>224</v>
+      </c>
+      <c r="C150" t="s">
+        <v>224</v>
+      </c>
+      <c r="F150" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>88</v>
+      </c>
+      <c r="B151" t="s">
+        <v>225</v>
+      </c>
+      <c r="C151" t="s">
+        <v>225</v>
+      </c>
+      <c r="F151" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>88</v>
+      </c>
+      <c r="B152" t="s">
+        <v>226</v>
+      </c>
+      <c r="C152" t="s">
+        <v>226</v>
+      </c>
+      <c r="F152" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>88</v>
+      </c>
+      <c r="B153" t="s">
+        <v>227</v>
+      </c>
+      <c r="C153" t="s">
+        <v>227</v>
+      </c>
+      <c r="F153" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>88</v>
+      </c>
+      <c r="B154" t="s">
+        <v>228</v>
+      </c>
+      <c r="C154" t="s">
+        <v>228</v>
+      </c>
+      <c r="F154" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>88</v>
+      </c>
+      <c r="B155" t="s">
+        <v>229</v>
+      </c>
+      <c r="C155" t="s">
+        <v>229</v>
+      </c>
+      <c r="F155" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>88</v>
+      </c>
+      <c r="B156" t="s">
+        <v>230</v>
+      </c>
+      <c r="C156" t="s">
+        <v>230</v>
+      </c>
+      <c r="F156" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>88</v>
+      </c>
+      <c r="B157" t="s">
+        <v>231</v>
+      </c>
+      <c r="C157" t="s">
+        <v>231</v>
+      </c>
+      <c r="F157" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>88</v>
+      </c>
+      <c r="B158" t="s">
+        <v>232</v>
+      </c>
+      <c r="C158" t="s">
+        <v>232</v>
+      </c>
+      <c r="F158" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>88</v>
+      </c>
+      <c r="B159" t="s">
+        <v>233</v>
+      </c>
+      <c r="C159" t="s">
+        <v>233</v>
+      </c>
+      <c r="F159" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2389,10 +3712,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>92</v>
